--- a/input/InputData.xlsx
+++ b/input/InputData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="商品マスタ" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="15">
   <si>
     <t xml:space="preserve">商品コード</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">入荷予定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出荷可能数累計</t>
   </si>
   <si>
     <t xml:space="preserve">前日末在庫</t>
@@ -162,23 +165,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -434,65 +437,65 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="8.41015625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>960</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>1152</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>576</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>200</v>
       </c>
     </row>
@@ -515,23 +518,23 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>50000</v>
+      <c r="B2" s="3" t="n">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
@@ -550,567 +553,696 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>46082</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="n">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>46083</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>46084</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>46085</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>60</v>
       </c>
+      <c r="E5" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="n">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>46086</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="n">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="n">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5" t="n">
+      <c r="A9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>46089</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="n">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>60</v>
       </c>
+      <c r="E10" s="5" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="n">
+      <c r="A11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>46091</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="5" t="n">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="4" t="n">
         <v>46092</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>60</v>
       </c>
+      <c r="E12" s="5" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="5" t="n">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5" t="n">
+      <c r="A14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4" t="n">
         <v>46094</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>72</v>
       </c>
+      <c r="E14" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="n">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="3" t="n">
+      <c r="A16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4" t="n">
         <v>46082</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="5" t="n">
+      <c r="A17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4" t="n">
         <v>46083</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <v>72</v>
       </c>
+      <c r="E17" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="5" t="n">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="4" t="n">
         <v>46084</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="5" t="n">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="4" t="n">
         <v>46085</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>72</v>
       </c>
+      <c r="E19" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="5" t="n">
+      <c r="A20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="4" t="n">
         <v>46086</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="5" t="n">
+      <c r="A21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="5" t="n">
         <v>72</v>
       </c>
+      <c r="E21" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="5" t="n">
+      <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="5" t="n">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="4" t="n">
         <v>46089</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>144</v>
       </c>
+      <c r="E23" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="5" t="n">
+      <c r="A24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="5" t="n">
+      <c r="A25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="4" t="n">
         <v>46091</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>144</v>
       </c>
+      <c r="E25" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="5" t="n">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="4" t="n">
         <v>46092</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="5" t="n">
         <v>60</v>
       </c>
+      <c r="E26" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="5" t="n">
+      <c r="A27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="5" t="n">
+      <c r="A28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="4" t="n">
         <v>46094</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="5" t="n">
+      <c r="A29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="5" t="n">
         <v>72</v>
       </c>
+      <c r="E29" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="3" t="n">
+      <c r="A30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="4" t="n">
         <v>46082</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="5" t="n">
+      <c r="A31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4" t="n">
         <v>46083</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="5" t="n">
+      <c r="A32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="4" t="n">
         <v>46084</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E32" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="5" t="n">
+      <c r="A33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="4" t="n">
         <v>46085</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E33" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="5" t="n">
+      <c r="A34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="4" t="n">
         <v>46086</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E34" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="5" t="n">
+      <c r="A35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E35" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="5" t="n">
+      <c r="A36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="5" t="n">
+      <c r="A37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="4" t="n">
         <v>46089</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E37" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="5" t="n">
+      <c r="A38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E38" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="5" t="n">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="4" t="n">
         <v>46091</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="5" t="n">
         <v>108</v>
       </c>
+      <c r="E39" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="5" t="n">
+      <c r="A40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="4" t="n">
         <v>46092</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="5" t="n">
+      <c r="A41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="5" t="n">
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="4" t="n">
         <v>46094</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="5" t="n">
         <v>36</v>
       </c>
+      <c r="E42" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="5" t="n">
+      <c r="A43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1132,34 +1264,34 @@
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>13</v>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>120</v>
       </c>
     </row>
